--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65368_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65368_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf2b532b1703a4e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rff3f3229584a4129"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4100</x:v>
+        <x:v>      2.3650</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65368_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65368_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rff3f3229584a4129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re344d3022bcd4598"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7075</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>18/08/2026</x:t>
         </x:is>
       </x:c>
